--- a/audit_reports/psyc_3020_package_audit_2026-04-05.xlsx
+++ b/audit_reports/psyc_3020_package_audit_2026-04-05.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{C2CF8FD2-2370-41E5-88B9-EF37B71AA5BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1104" yWindow="-15780" windowWidth="37536" windowHeight="9180" xr2:uid="{DA2C4B1E-D09D-4C16-8EE6-37C213DAB76C}"/>
+    <workbookView xWindow="2064" yWindow="-16884" windowWidth="18228" windowHeight="8316" xr2:uid="{DA2C4B1E-D09D-4C16-8EE6-37C213DAB76C}"/>
   </bookViews>
   <sheets>
     <sheet name="psyc_3020_package_audit_2026-04" sheetId="1" r:id="rId1"/>
